--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.7698947050117</v>
+        <v>4.675107889564402</v>
       </c>
       <c r="D2" t="n">
-        <v>25.62565553653915</v>
+        <v>4.164169024687612</v>
       </c>
       <c r="E2" t="n">
-        <v>10.64786433253248</v>
+        <v>1.730277954036527</v>
       </c>
       <c r="F2" t="n">
-        <v>13.854796837629</v>
+        <v>2.251404486114713</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.98382043985026</v>
+        <v>1.784870821475667</v>
       </c>
       <c r="D3" t="n">
-        <v>11.04021835867795</v>
+        <v>1.794035483285167</v>
       </c>
       <c r="E3" t="n">
-        <v>10.64786433253248</v>
+        <v>1.730277954036527</v>
       </c>
       <c r="F3" t="n">
-        <v>13.854796837629</v>
+        <v>2.251404486114713</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.973984369181242</v>
+        <v>1.458272459991952</v>
       </c>
       <c r="D4" t="n">
-        <v>8.736200513937662</v>
+        <v>1.41963258351487</v>
       </c>
       <c r="E4" t="n">
-        <v>10.64786433253248</v>
+        <v>1.730277954036527</v>
       </c>
       <c r="F4" t="n">
-        <v>13.854796837629</v>
+        <v>2.251404486114713</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.3097616985381</v>
+        <v>4.925336276012442</v>
       </c>
       <c r="D5" t="n">
-        <v>30.24938067745983</v>
+        <v>4.915524360087223</v>
       </c>
       <c r="E5" t="n">
-        <v>10.64786433253248</v>
+        <v>1.730277954036527</v>
       </c>
       <c r="F5" t="n">
-        <v>13.854796837629</v>
+        <v>2.251404486114713</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.52050906434557</v>
+        <v>6.422082722956155</v>
       </c>
       <c r="D6" t="n">
-        <v>39.19984462456376</v>
+        <v>6.369974751491611</v>
       </c>
       <c r="E6" t="n">
-        <v>10.64786433253248</v>
+        <v>1.730277954036527</v>
       </c>
       <c r="F6" t="n">
-        <v>13.854796837629</v>
+        <v>2.251404486114713</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.41799073786588</v>
+        <v>3.480423494903206</v>
       </c>
       <c r="D7" t="n">
-        <v>8.100543692155489</v>
+        <v>1.316338349975267</v>
       </c>
       <c r="E7" t="n">
-        <v>10.64786433253248</v>
+        <v>1.730277954036527</v>
       </c>
       <c r="F7" t="n">
-        <v>13.854796837629</v>
+        <v>2.251404486114713</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.63406011768428</v>
+        <v>5.465534769123695</v>
       </c>
       <c r="D8" t="n">
-        <v>44.42737875578354</v>
+        <v>7.219449047814825</v>
       </c>
       <c r="E8" t="n">
-        <v>10.64786433253248</v>
+        <v>1.730277954036527</v>
       </c>
       <c r="F8" t="n">
-        <v>13.854796837629</v>
+        <v>2.251404486114713</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
